--- a/tareas/seguimiento.xlsx
+++ b/tareas/seguimiento.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="tarea_2" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="elementos generales" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="tarea_3" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="15">
   <si>
     <t xml:space="preserve">ci</t>
   </si>
@@ -48,20 +49,40 @@
   </si>
   <si>
     <t xml:space="preserve">jonathan y diego tarea similares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">muy bien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chévere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">usa fuentes para los códigos y no indica cuáles son. Aplica las funciones de forma distinta a lo solicitado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">algunas fallas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">muy ordenado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ordenada y analítica</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
   <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -121,8 +142,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -252,230 +281,230 @@
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="58.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="58.08"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>26260451</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>27222651</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>27487707</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="0" t="s">
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>27531901</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="0" t="s">
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>27600050</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="0" t="s">
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>27660553</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="0" t="s">
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>27669710</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>27988203</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="0" t="s">
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>28210812</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="0" t="s">
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>28306246</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="0" t="s">
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>29521323</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="0" t="s">
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>29658512</v>
       </c>
-      <c r="B13" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="0" t="s">
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>29686193</v>
       </c>
-      <c r="B14" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="0" t="s">
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>29756414</v>
       </c>
-      <c r="B15" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="0" t="s">
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>29765256</v>
       </c>
-      <c r="B16" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="0" t="s">
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>30037872</v>
       </c>
-      <c r="B17" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="0" t="s">
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>30138648</v>
       </c>
-      <c r="B18" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="0" t="s">
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>27995146</v>
       </c>
-      <c r="B19" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="0" t="s">
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -499,9 +528,270 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.64"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="n">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>27222651</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>27487707</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>27531901</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>27600050</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>27660553</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>27669710</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>27988203</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>27995146</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>28210812</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>28306246</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>29521323</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>29658512</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>29686193</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>29756414</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>30037872</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>30138648</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
